--- a/GeogameUpdater/Currentmodels/GeogameTrainingProgramming/GameAssets/geodata.xlsx
+++ b/GeogameUpdater/Currentmodels/GeogameTrainingProgramming/GameAssets/geodata.xlsx
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="AW2" s="9" t="n">
-        <v>4010</v>
+        <v>0</v>
       </c>
       <c r="AX2" s="9" t="n">
         <v>0.1</v>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="AW3" t="n">
-        <v>3740</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
         <v>0.1</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="AW4" s="10" t="n">
-        <v>3610</v>
+        <v>0</v>
       </c>
       <c r="AX4" s="10" t="n">
         <v>0.1</v>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
         <v>0.1</v>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="AW6" s="11" t="n">
-        <v>2970</v>
+        <v>0</v>
       </c>
       <c r="AX6" s="11" t="n">
         <v>0.1</v>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>3140</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
         <v>0.1</v>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="AW12" s="13" t="n">
-        <v>3190</v>
+        <v>0</v>
       </c>
       <c r="AX12" s="13" t="n">
         <v>0.1</v>
